--- a/astro-site/public/dl/ice-cream-shop-checklist-templates/06-ice-cream-shop-seasonal-catering-checklists.xlsx
+++ b/astro-site/public/dl/ice-cream-shop-checklist-templates/06-ice-cream-shop-seasonal-catering-checklists.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Reinforce the team: hire 2 weeks before the season (minors 14–15: FLSA hour and equipment limits; check state work permits)</t>
+          <t>Reinforce the team: hire in March–April so the summer team is trained by Memorial Day. Minors 14–15: FLSA hours, no work inside freezers beyond stepping in to grab an item, and no operating or cleaning the batch freezer, pasteurizer or other power-driven machines (29 CFR 570.33); check state work permits</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Prepare to-go packaging: pints and quarts (pre-packed pints get an allergen label; selling by weight needs a legal-for-trade scale)</t>
+          <t>Prepare to-go packaging: pints and quarts. Pints packed ahead for the freezer case carry a label: flavor name, ingredients, allergens, net weight and your shop's name and city (FDA Food Code 3-602.11); hand-packed to order they are not "packaged". Selling by weight needs a legal-for-trade scale</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Get guests' allergies and intolerances IN WRITING and confirm which flavors you can serve: an ice cream menu concentrates MILK, TREE NUTS, EGG, WHEAT (cones, wafers, cookies), SOY and SESAME (9 major allergens; UK: 14)</t>
+          <t>Get guests' allergies and intolerances IN WRITING and confirm which flavors you can serve: an ice cream menu concentrates MILK, TREE NUTS, PEANUTS, EGG, WHEAT (cones, wafers, cookies), SOY and SESAME (US: 9 major allergens; UK: 14)</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Pack the off-site service kit: pans, spades, gloves, napkins</t>
+          <t>Pack the off-site service kit: pans, one scoop per flavor (no running-water dipper well on site), spades, gloves, napkins and a probe thermometer</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Check the cold chain for transport (insulated carriers; dry ice with gloves, never touching the ice cream, vehicle ventilated)</t>
+          <t>Check the cold chain for transport (insulated carriers; dry ice with gloves, never touching the ice cream, vehicle ventilated). Dry ice over-hardens the ice cream: let the pans temper before scooping</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Serve ice cream keeping the presentation and flavor rotation</t>
+          <t>Serve from a dipping cart or a dry-ice cooler, scoops kept in their pan with the handle up (FDA Food Code 3-304.12(A)); check temps during service and throw out any ice cream that melts — never refreeze it — log reading: ____ °F</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
